--- a/Письма от заказчика/Ведомость проверки результатов РД АСУ ТП 10.10.2025 (50495598 v1).XLSX
+++ b/Письма от заказчика/Ведомость проверки результатов РД АСУ ТП 10.10.2025 (50495598 v1).XLSX
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\VLA\AD01\Projects\Реконструкция ИвТЭЦ-2 v2.0\3. Корреспонденция\6.Редактируемые письма и СЗ\Письма\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Projects\380-25_Ivanovo_TEC\Письма от заказчика\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D837DD-081F-4540-9FAF-ECD15A804B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОТР-ПД-РД" sheetId="1" r:id="rId1"/>
@@ -122,15 +123,15 @@
     <definedName name="Статус1">'ОТР-ПД-РД'!$B$130:$C$132</definedName>
     <definedName name="Статус2">'ОТР-ПД-РД'!$B$135:$C$136</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Батуева Дарья Александровна - Личное представление" guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
+    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
+    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
     <customWorkbookView name="Неганов Евгений Валерьевич - Личное представление" guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" mergeInterval="0" personalView="1" maximized="1" xWindow="-11" yWindow="-11" windowWidth="2582" windowHeight="1402" activeSheetId="1"/>
-    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
-    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
-    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Батуева Дарья Александровна - Личное представление" guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -152,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="256">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -1260,11 +1261,17 @@
 2. Не выработаны технические решения по  интеграции АСУ ТП/ВК с верхнеуровневыми системами типа ОИК ВФ "ПАО Т Плюс", системой Диспетчерского контроля и управления ИвГТС.     
 3. Не выработаны и не согласованы с ЦИБ ПАО "Т Плюс" технические решения по обеспечению информационной безопасности АСУ ТП/ВК. Выроботать и согласовать с ЦИБ ПАО "Т Плюс".</t>
   </si>
+  <si>
+    <t>Исправлен KKS АРМ-ЭТО и принтера.</t>
+  </si>
+  <si>
+    <t>На 3 листе добавил KKS котлов. На 15, 16, 24 листах добавил KKS сигналов параметров насосов и самих насосов. На 25 не увидел какие KKS ещё добавить, если нужны KKS насосов, я их нигде не нашёл, в средний и верхний уровень сигналы никакие не поступают. На 28 добавил KKS котлов и дисковых затворов перед котлами. Если требуется отмаркировать ещё какое-либо оборудование, прошу указать конкретные позиции. Все KKS сигналы, описанные под схемами в таблице, на схемах присутствуют.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1602,7 +1609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1832,37 +1839,60 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1876,38 +1906,17 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1936,66 +1945,31 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="14">
     <dxf>
@@ -2259,20 +2233,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="B130:B134" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="B130:B134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица3" displayName="Таблица3" ref="B130:B134" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="B130:B134" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="Столбец1" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Столбец1" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица36" displayName="Таблица36" ref="B21:B25" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
-  <autoFilter ref="B21:B25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица36" displayName="Таблица36" ref="B21:B25" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="B21:B25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="Столбец1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Столбец1" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2574,7 +2548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2636,13 +2610,13 @@
       <c r="X1" s="3"/>
     </row>
     <row r="2" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -2664,13 +2638,13 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
       <c r="H3" s="30"/>
@@ -2692,12 +2666,12 @@
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="48"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -2720,12 +2694,12 @@
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
       <c r="E5" s="48"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -2802,44 +2776,44 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:256" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="92" t="s">
+      <c r="D8" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="92" t="s">
+      <c r="F8" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="92" t="s">
+      <c r="G8" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="92" t="s">
+      <c r="H8" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="95" t="s">
+      <c r="I8" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="95"/>
-      <c r="L8" s="92" t="s">
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="92"/>
-      <c r="N8" s="95" t="s">
+      <c r="M8" s="93"/>
+      <c r="N8" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="95"/>
-      <c r="P8" s="89" t="s">
+      <c r="O8" s="94"/>
+      <c r="P8" s="97" t="s">
         <v>46</v>
       </c>
       <c r="Q8" s="34" t="s">
@@ -2864,14 +2838,14 @@
       </c>
     </row>
     <row r="9" spans="1:256" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
+      <c r="A9" s="99"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
       <c r="I9" s="25" t="s">
         <v>29</v>
       </c>
@@ -2893,7 +2867,7 @@
       <c r="O9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="90"/>
+      <c r="P9" s="98"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="35" t="s">
         <v>6</v>
@@ -2914,29 +2888,29 @@
       </c>
     </row>
     <row r="10" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="86" t="s">
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="87" t="s">
+      <c r="J10" s="103"/>
+      <c r="K10" s="103"/>
+      <c r="L10" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="87"/>
-      <c r="N10" s="86" t="s">
+      <c r="M10" s="102"/>
+      <c r="N10" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="86"/>
+      <c r="O10" s="103"/>
       <c r="P10" s="47" t="s">
         <v>17</v>
       </c>
@@ -3523,8 +3497,12 @@
       <c r="M13" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="N13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>254</v>
+      </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="38"/>
       <c r="R13" s="36"/>
@@ -3767,7 +3745,7 @@
       <c r="IU13" s="40"/>
       <c r="IV13" s="40"/>
     </row>
-    <row r="14" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:256" s="37" customFormat="1" ht="142.5" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>3</v>
       </c>
@@ -3803,8 +3781,12 @@
       <c r="M14" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
+      <c r="N14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>255</v>
+      </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="38"/>
       <c r="R14" s="36"/>
@@ -7392,7 +7374,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="6"/>
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="24" t="s">
         <v>90</v>
       </c>
       <c r="D27" s="6"/>
@@ -7683,7 +7665,7 @@
       <c r="I28" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="93" t="s">
+      <c r="J28" s="100" t="s">
         <v>106</v>
       </c>
       <c r="K28" s="43" t="s">
@@ -7961,7 +7943,7 @@
       <c r="I29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J29" s="94"/>
+      <c r="J29" s="101"/>
       <c r="K29" s="43" t="s">
         <v>103</v>
       </c>
@@ -9315,7 +9297,7 @@
       <c r="IU33" s="40"/>
       <c r="IV33" s="40"/>
     </row>
-    <row r="34" spans="1:256" s="37" customFormat="1" ht="114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:256" s="37" customFormat="1" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>23</v>
       </c>
@@ -9613,7 +9595,7 @@
       <c r="I35" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="93"/>
+      <c r="J35" s="100"/>
       <c r="K35" s="43" t="s">
         <v>103</v>
       </c>
@@ -9887,7 +9869,7 @@
       <c r="I36" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="94"/>
+      <c r="J36" s="101"/>
       <c r="K36" s="43" t="s">
         <v>103</v>
       </c>
@@ -10414,29 +10396,29 @@
       <c r="IV37" s="40"/>
     </row>
     <row r="38" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="87" t="s">
+      <c r="A38" s="102" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="86" t="s">
+      <c r="B38" s="102"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="87" t="s">
+      <c r="J38" s="103"/>
+      <c r="K38" s="103"/>
+      <c r="L38" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="87"/>
-      <c r="N38" s="86" t="s">
+      <c r="M38" s="102"/>
+      <c r="N38" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="O38" s="86"/>
+      <c r="O38" s="103"/>
       <c r="P38" s="47" t="s">
         <v>17</v>
       </c>
@@ -10681,30 +10663,30 @@
       <c r="IU38" s="40"/>
       <c r="IV38" s="40"/>
     </row>
-    <row r="39" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>1</v>
       </c>
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="80"/>
-      <c r="E39" s="81" t="s">
+      <c r="D39" s="6"/>
+      <c r="E39" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="82" t="s">
+      <c r="F39" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G39" s="83" t="s">
+      <c r="G39" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H39" s="84" t="s">
+      <c r="H39" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I39" s="85"/>
+      <c r="I39" s="17"/>
       <c r="J39" s="77"/>
       <c r="K39" s="43"/>
       <c r="L39" s="16"/>
@@ -10957,24 +10939,24 @@
       <c r="A40" s="6">
         <v>2</v>
       </c>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="80"/>
-      <c r="E40" s="81" t="s">
+      <c r="D40" s="6"/>
+      <c r="E40" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F40" s="82"/>
-      <c r="G40" s="83" t="s">
+      <c r="F40" s="46"/>
+      <c r="G40" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="84" t="s">
+      <c r="H40" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I40" s="85"/>
+      <c r="I40" s="17"/>
       <c r="J40" s="77"/>
       <c r="K40" s="43"/>
       <c r="L40" s="16"/>
@@ -11227,24 +11209,24 @@
       <c r="A41" s="6">
         <v>3</v>
       </c>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D41" s="80"/>
-      <c r="E41" s="81" t="s">
+      <c r="D41" s="6"/>
+      <c r="E41" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F41" s="82"/>
-      <c r="G41" s="83" t="s">
+      <c r="F41" s="46"/>
+      <c r="G41" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H41" s="84" t="s">
+      <c r="H41" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I41" s="85"/>
+      <c r="I41" s="17"/>
       <c r="J41" s="77"/>
       <c r="K41" s="43"/>
       <c r="L41" s="16"/>
@@ -11497,24 +11479,24 @@
       <c r="A42" s="6">
         <v>4</v>
       </c>
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D42" s="80"/>
-      <c r="E42" s="81" t="s">
+      <c r="D42" s="6"/>
+      <c r="E42" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F42" s="82"/>
-      <c r="G42" s="83" t="s">
+      <c r="F42" s="46"/>
+      <c r="G42" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H42" s="84" t="s">
+      <c r="H42" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I42" s="85"/>
+      <c r="I42" s="17"/>
       <c r="J42" s="77"/>
       <c r="K42" s="43"/>
       <c r="L42" s="16"/>
@@ -11767,24 +11749,24 @@
       <c r="A43" s="6">
         <v>5</v>
       </c>
-      <c r="B43" s="80" t="s">
+      <c r="B43" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="80"/>
-      <c r="E43" s="81" t="s">
+      <c r="D43" s="6"/>
+      <c r="E43" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F43" s="82"/>
-      <c r="G43" s="83" t="s">
+      <c r="F43" s="46"/>
+      <c r="G43" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H43" s="84" t="s">
+      <c r="H43" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I43" s="85"/>
+      <c r="I43" s="17"/>
       <c r="J43" s="77"/>
       <c r="K43" s="43"/>
       <c r="L43" s="16"/>
@@ -12037,24 +12019,24 @@
       <c r="A44" s="6">
         <v>6</v>
       </c>
-      <c r="B44" s="80" t="s">
+      <c r="B44" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D44" s="80"/>
-      <c r="E44" s="81" t="s">
+      <c r="D44" s="6"/>
+      <c r="E44" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="F44" s="82"/>
-      <c r="G44" s="83" t="s">
+      <c r="F44" s="46"/>
+      <c r="G44" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="84" t="s">
+      <c r="H44" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I44" s="85"/>
+      <c r="I44" s="17"/>
       <c r="J44" s="77"/>
       <c r="K44" s="43"/>
       <c r="L44" s="16"/>
@@ -12307,24 +12289,24 @@
       <c r="A45" s="6">
         <v>7</v>
       </c>
-      <c r="B45" s="80" t="s">
+      <c r="B45" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D45" s="80"/>
-      <c r="E45" s="81" t="s">
+      <c r="D45" s="6"/>
+      <c r="E45" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F45" s="82"/>
-      <c r="G45" s="83" t="s">
+      <c r="F45" s="46"/>
+      <c r="G45" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="84" t="s">
+      <c r="H45" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I45" s="85"/>
+      <c r="I45" s="17"/>
       <c r="J45" s="77"/>
       <c r="K45" s="43"/>
       <c r="L45" s="16"/>
@@ -12577,24 +12559,24 @@
       <c r="A46" s="6">
         <v>8</v>
       </c>
-      <c r="B46" s="80" t="s">
+      <c r="B46" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="80"/>
-      <c r="E46" s="81" t="s">
+      <c r="D46" s="6"/>
+      <c r="E46" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="82"/>
-      <c r="G46" s="83" t="s">
+      <c r="F46" s="46"/>
+      <c r="G46" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H46" s="84" t="s">
+      <c r="H46" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="85"/>
+      <c r="I46" s="17"/>
       <c r="J46" s="77"/>
       <c r="K46" s="43"/>
       <c r="L46" s="16"/>
@@ -12843,28 +12825,28 @@
       <c r="IU46" s="40"/>
       <c r="IV46" s="40"/>
     </row>
-    <row r="47" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>9</v>
       </c>
-      <c r="B47" s="80" t="s">
+      <c r="B47" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C47" s="79" t="s">
+      <c r="C47" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="D47" s="80"/>
-      <c r="E47" s="81" t="s">
+      <c r="D47" s="6"/>
+      <c r="E47" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="82"/>
-      <c r="G47" s="83" t="s">
+      <c r="F47" s="46"/>
+      <c r="G47" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H47" s="84" t="s">
+      <c r="H47" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I47" s="85"/>
+      <c r="I47" s="17"/>
       <c r="J47" s="77"/>
       <c r="K47" s="43"/>
       <c r="L47" s="16"/>
@@ -13113,28 +13095,28 @@
       <c r="IU47" s="40"/>
       <c r="IV47" s="40"/>
     </row>
-    <row r="48" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>10</v>
       </c>
-      <c r="B48" s="80" t="s">
+      <c r="B48" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="80"/>
-      <c r="E48" s="81" t="s">
+      <c r="D48" s="6"/>
+      <c r="E48" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="F48" s="82"/>
-      <c r="G48" s="83" t="s">
+      <c r="F48" s="46"/>
+      <c r="G48" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H48" s="84" t="s">
+      <c r="H48" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="85"/>
+      <c r="I48" s="17"/>
       <c r="J48" s="77"/>
       <c r="K48" s="43"/>
       <c r="L48" s="16"/>
@@ -13387,24 +13369,24 @@
       <c r="A49" s="6">
         <v>11</v>
       </c>
-      <c r="B49" s="80" t="s">
+      <c r="B49" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C49" s="79" t="s">
+      <c r="C49" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="D49" s="80"/>
-      <c r="E49" s="81" t="s">
+      <c r="D49" s="6"/>
+      <c r="E49" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F49" s="82"/>
-      <c r="G49" s="83" t="s">
+      <c r="F49" s="46"/>
+      <c r="G49" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H49" s="84" t="s">
+      <c r="H49" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I49" s="85"/>
+      <c r="I49" s="17"/>
       <c r="J49" s="77"/>
       <c r="K49" s="43"/>
       <c r="L49" s="16"/>
@@ -13653,28 +13635,28 @@
       <c r="IU49" s="40"/>
       <c r="IV49" s="40"/>
     </row>
-    <row r="50" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:256" s="37" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>12</v>
       </c>
-      <c r="B50" s="80" t="s">
+      <c r="B50" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="79" t="s">
+      <c r="C50" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="D50" s="80"/>
-      <c r="E50" s="81" t="s">
+      <c r="D50" s="6"/>
+      <c r="E50" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F50" s="82"/>
-      <c r="G50" s="83" t="s">
+      <c r="F50" s="46"/>
+      <c r="G50" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H50" s="84" t="s">
+      <c r="H50" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I50" s="85"/>
+      <c r="I50" s="17"/>
       <c r="J50" s="77"/>
       <c r="K50" s="43"/>
       <c r="L50" s="16"/>
@@ -13927,24 +13909,24 @@
       <c r="A51" s="6">
         <v>13</v>
       </c>
-      <c r="B51" s="80" t="s">
+      <c r="B51" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D51" s="80"/>
-      <c r="E51" s="81" t="s">
+      <c r="D51" s="6"/>
+      <c r="E51" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F51" s="82"/>
-      <c r="G51" s="83" t="s">
+      <c r="F51" s="46"/>
+      <c r="G51" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H51" s="84" t="s">
+      <c r="H51" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I51" s="85"/>
+      <c r="I51" s="17"/>
       <c r="J51" s="77"/>
       <c r="K51" s="43"/>
       <c r="L51" s="16"/>
@@ -14197,24 +14179,24 @@
       <c r="A52" s="6">
         <v>14</v>
       </c>
-      <c r="B52" s="80" t="s">
+      <c r="B52" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C52" s="79" t="s">
+      <c r="C52" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D52" s="80"/>
-      <c r="E52" s="81" t="s">
+      <c r="D52" s="6"/>
+      <c r="E52" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F52" s="82"/>
-      <c r="G52" s="83" t="s">
+      <c r="F52" s="46"/>
+      <c r="G52" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="84" t="s">
+      <c r="H52" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I52" s="85"/>
+      <c r="I52" s="17"/>
       <c r="J52" s="77"/>
       <c r="K52" s="43"/>
       <c r="L52" s="16"/>
@@ -14467,24 +14449,24 @@
       <c r="A53" s="6">
         <v>15</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="79" t="s">
+      <c r="C53" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D53" s="80"/>
-      <c r="E53" s="81" t="s">
+      <c r="D53" s="6"/>
+      <c r="E53" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F53" s="82"/>
-      <c r="G53" s="83" t="s">
+      <c r="F53" s="46"/>
+      <c r="G53" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H53" s="84" t="s">
+      <c r="H53" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I53" s="85"/>
+      <c r="I53" s="17"/>
       <c r="J53" s="77"/>
       <c r="K53" s="43"/>
       <c r="L53" s="16"/>
@@ -14737,24 +14719,24 @@
       <c r="A54" s="6">
         <v>16</v>
       </c>
-      <c r="B54" s="80" t="s">
+      <c r="B54" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C54" s="79" t="s">
+      <c r="C54" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="80"/>
-      <c r="E54" s="81" t="s">
+      <c r="D54" s="6"/>
+      <c r="E54" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F54" s="82"/>
-      <c r="G54" s="83" t="s">
+      <c r="F54" s="46"/>
+      <c r="G54" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H54" s="84" t="s">
+      <c r="H54" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I54" s="85"/>
+      <c r="I54" s="17"/>
       <c r="J54" s="77"/>
       <c r="K54" s="43"/>
       <c r="L54" s="16"/>
@@ -15007,24 +14989,24 @@
       <c r="A55" s="6">
         <v>17</v>
       </c>
-      <c r="B55" s="80" t="s">
+      <c r="B55" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="D55" s="80"/>
-      <c r="E55" s="81" t="s">
+      <c r="D55" s="6"/>
+      <c r="E55" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="82"/>
-      <c r="G55" s="83" t="s">
+      <c r="F55" s="46"/>
+      <c r="G55" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H55" s="84" t="s">
+      <c r="H55" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I55" s="85"/>
+      <c r="I55" s="17"/>
       <c r="J55" s="77"/>
       <c r="K55" s="43"/>
       <c r="L55" s="16"/>
@@ -15277,24 +15259,24 @@
       <c r="A56" s="6">
         <v>18</v>
       </c>
-      <c r="B56" s="80" t="s">
+      <c r="B56" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C56" s="79" t="s">
+      <c r="C56" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="80"/>
-      <c r="E56" s="81" t="s">
+      <c r="D56" s="6"/>
+      <c r="E56" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="82"/>
-      <c r="G56" s="83" t="s">
+      <c r="F56" s="46"/>
+      <c r="G56" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H56" s="84" t="s">
+      <c r="H56" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I56" s="85"/>
+      <c r="I56" s="17"/>
       <c r="J56" s="77"/>
       <c r="K56" s="43"/>
       <c r="L56" s="16"/>
@@ -15547,24 +15529,24 @@
       <c r="A57" s="6">
         <v>19</v>
       </c>
-      <c r="B57" s="80" t="s">
+      <c r="B57" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C57" s="79" t="s">
+      <c r="C57" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="80"/>
-      <c r="E57" s="81" t="s">
+      <c r="D57" s="6"/>
+      <c r="E57" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="82"/>
-      <c r="G57" s="83" t="s">
+      <c r="F57" s="46"/>
+      <c r="G57" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="84" t="s">
+      <c r="H57" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="85"/>
+      <c r="I57" s="17"/>
       <c r="J57" s="77"/>
       <c r="K57" s="43"/>
       <c r="L57" s="16"/>
@@ -15813,28 +15795,28 @@
       <c r="IU57" s="40"/>
       <c r="IV57" s="40"/>
     </row>
-    <row r="58" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>20</v>
       </c>
-      <c r="B58" s="80" t="s">
+      <c r="B58" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C58" s="79" t="s">
+      <c r="C58" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="D58" s="80"/>
-      <c r="E58" s="81" t="s">
+      <c r="D58" s="6"/>
+      <c r="E58" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F58" s="82"/>
-      <c r="G58" s="83" t="s">
+      <c r="F58" s="46"/>
+      <c r="G58" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H58" s="84" t="s">
+      <c r="H58" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I58" s="85"/>
+      <c r="I58" s="17"/>
       <c r="J58" s="77"/>
       <c r="K58" s="43"/>
       <c r="L58" s="16"/>
@@ -16087,24 +16069,24 @@
       <c r="A59" s="6">
         <v>21</v>
       </c>
-      <c r="B59" s="80" t="s">
+      <c r="B59" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="79" t="s">
+      <c r="C59" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="80"/>
-      <c r="E59" s="81" t="s">
+      <c r="D59" s="6"/>
+      <c r="E59" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F59" s="82"/>
-      <c r="G59" s="83" t="s">
+      <c r="F59" s="46"/>
+      <c r="G59" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H59" s="84" t="s">
+      <c r="H59" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I59" s="85"/>
+      <c r="I59" s="17"/>
       <c r="J59" s="77"/>
       <c r="K59" s="43"/>
       <c r="L59" s="16"/>
@@ -16353,28 +16335,28 @@
       <c r="IU59" s="40"/>
       <c r="IV59" s="40"/>
     </row>
-    <row r="60" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>22</v>
       </c>
-      <c r="B60" s="80"/>
-      <c r="C60" s="79" t="s">
+      <c r="B60" s="6"/>
+      <c r="C60" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="80"/>
-      <c r="E60" s="81" t="s">
+      <c r="D60" s="6"/>
+      <c r="E60" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F60" s="82" t="s">
+      <c r="F60" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G60" s="83" t="s">
+      <c r="G60" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H60" s="84" t="s">
+      <c r="H60" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I60" s="85"/>
+      <c r="I60" s="17"/>
       <c r="J60" s="77"/>
       <c r="K60" s="43"/>
       <c r="L60" s="16"/>
@@ -16623,28 +16605,28 @@
       <c r="IU60" s="40"/>
       <c r="IV60" s="40"/>
     </row>
-    <row r="61" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>23</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="79" t="s">
+      <c r="B61" s="6"/>
+      <c r="C61" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="80"/>
-      <c r="E61" s="81" t="s">
+      <c r="D61" s="6"/>
+      <c r="E61" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F61" s="82" t="s">
+      <c r="F61" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G61" s="83" t="s">
+      <c r="G61" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H61" s="84" t="s">
+      <c r="H61" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I61" s="85"/>
+      <c r="I61" s="17"/>
       <c r="J61" s="77"/>
       <c r="K61" s="43"/>
       <c r="L61" s="16"/>
@@ -16893,28 +16875,28 @@
       <c r="IU61" s="40"/>
       <c r="IV61" s="40"/>
     </row>
-    <row r="62" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>24</v>
       </c>
-      <c r="B62" s="80"/>
-      <c r="C62" s="79" t="s">
+      <c r="B62" s="6"/>
+      <c r="C62" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="D62" s="80"/>
-      <c r="E62" s="81" t="s">
+      <c r="D62" s="6"/>
+      <c r="E62" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F62" s="82" t="s">
+      <c r="F62" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G62" s="83" t="s">
+      <c r="G62" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="84" t="s">
+      <c r="H62" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I62" s="85"/>
+      <c r="I62" s="17"/>
       <c r="J62" s="77"/>
       <c r="K62" s="43"/>
       <c r="L62" s="16"/>
@@ -17163,28 +17145,28 @@
       <c r="IU62" s="40"/>
       <c r="IV62" s="40"/>
     </row>
-    <row r="63" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>25</v>
       </c>
-      <c r="B63" s="80"/>
-      <c r="C63" s="79" t="s">
+      <c r="B63" s="6"/>
+      <c r="C63" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="D63" s="80"/>
-      <c r="E63" s="81" t="s">
+      <c r="D63" s="6"/>
+      <c r="E63" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F63" s="82" t="s">
+      <c r="F63" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G63" s="83" t="s">
+      <c r="G63" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H63" s="84" t="s">
+      <c r="H63" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I63" s="85"/>
+      <c r="I63" s="17"/>
       <c r="J63" s="77"/>
       <c r="K63" s="43"/>
       <c r="L63" s="16"/>
@@ -17433,28 +17415,28 @@
       <c r="IU63" s="40"/>
       <c r="IV63" s="40"/>
     </row>
-    <row r="64" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>26</v>
       </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="79" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="D64" s="80"/>
-      <c r="E64" s="81" t="s">
+      <c r="D64" s="6"/>
+      <c r="E64" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F64" s="82" t="s">
+      <c r="F64" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G64" s="83" t="s">
+      <c r="G64" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H64" s="84" t="s">
+      <c r="H64" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I64" s="85"/>
+      <c r="I64" s="17"/>
       <c r="J64" s="77"/>
       <c r="K64" s="43"/>
       <c r="L64" s="16"/>
@@ -17703,28 +17685,28 @@
       <c r="IU64" s="40"/>
       <c r="IV64" s="40"/>
     </row>
-    <row r="65" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>27</v>
       </c>
-      <c r="B65" s="80"/>
-      <c r="C65" s="79" t="s">
+      <c r="B65" s="6"/>
+      <c r="C65" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="D65" s="80"/>
-      <c r="E65" s="81" t="s">
+      <c r="D65" s="6"/>
+      <c r="E65" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="82" t="s">
+      <c r="F65" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="G65" s="83" t="s">
+      <c r="G65" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H65" s="84" t="s">
+      <c r="H65" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="85"/>
+      <c r="I65" s="17"/>
       <c r="J65" s="77"/>
       <c r="K65" s="43"/>
       <c r="L65" s="16"/>
@@ -17974,29 +17956,29 @@
       <c r="IV65" s="40"/>
     </row>
     <row r="66" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="87" t="s">
+      <c r="A66" s="102" t="s">
         <v>163</v>
       </c>
-      <c r="B66" s="87"/>
-      <c r="C66" s="87"/>
-      <c r="D66" s="87"/>
-      <c r="E66" s="87"/>
-      <c r="F66" s="87"/>
-      <c r="G66" s="87"/>
-      <c r="H66" s="87"/>
-      <c r="I66" s="86" t="s">
+      <c r="B66" s="102"/>
+      <c r="C66" s="102"/>
+      <c r="D66" s="102"/>
+      <c r="E66" s="102"/>
+      <c r="F66" s="102"/>
+      <c r="G66" s="102"/>
+      <c r="H66" s="102"/>
+      <c r="I66" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="86"/>
-      <c r="K66" s="86"/>
-      <c r="L66" s="87" t="s">
+      <c r="J66" s="103"/>
+      <c r="K66" s="103"/>
+      <c r="L66" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="M66" s="87"/>
-      <c r="N66" s="86" t="s">
+      <c r="M66" s="102"/>
+      <c r="N66" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="O66" s="86"/>
+      <c r="O66" s="103"/>
       <c r="P66" s="47" t="s">
         <v>17</v>
       </c>
@@ -18241,27 +18223,27 @@
       <c r="IU66" s="40"/>
       <c r="IV66" s="40"/>
     </row>
-    <row r="67" spans="1:256" s="37" customFormat="1" ht="156.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:256" s="37" customFormat="1" ht="185.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>1</v>
       </c>
-      <c r="B67" s="124" t="s">
+      <c r="B67" s="84" t="s">
         <v>165</v>
       </c>
-      <c r="C67" s="125" t="s">
+      <c r="C67" s="88" t="s">
         <v>157</v>
       </c>
-      <c r="D67" s="124"/>
-      <c r="E67" s="126" t="s">
+      <c r="D67" s="84"/>
+      <c r="E67" s="89" t="s">
         <v>164</v>
       </c>
-      <c r="F67" s="82" t="s">
+      <c r="F67" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="83" t="s">
+      <c r="G67" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H67" s="84" t="s">
+      <c r="H67" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I67" s="17"/>
@@ -18517,23 +18499,23 @@
       <c r="A68" s="6">
         <v>2</v>
       </c>
-      <c r="B68" s="124" t="s">
+      <c r="B68" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="C68" s="125" t="s">
+      <c r="C68" s="88" t="s">
         <v>167</v>
       </c>
-      <c r="D68" s="124" t="s">
+      <c r="D68" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="E68" s="127" t="s">
+      <c r="E68" s="89" t="s">
         <v>169</v>
       </c>
       <c r="F68" s="46"/>
-      <c r="G68" s="83" t="s">
+      <c r="G68" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H68" s="84" t="s">
+      <c r="H68" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I68" s="17"/>
@@ -18789,23 +18771,23 @@
       <c r="A69" s="6">
         <v>3</v>
       </c>
-      <c r="B69" s="124" t="s">
+      <c r="B69" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="C69" s="125" t="s">
+      <c r="C69" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="D69" s="124" t="s">
+      <c r="D69" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="E69" s="127" t="s">
+      <c r="E69" s="89" t="s">
         <v>107</v>
       </c>
       <c r="F69" s="46"/>
-      <c r="G69" s="83" t="s">
+      <c r="G69" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H69" s="84" t="s">
+      <c r="H69" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I69" s="17"/>
@@ -19061,23 +19043,23 @@
       <c r="A70" s="6">
         <v>4</v>
       </c>
-      <c r="B70" s="124" t="s">
+      <c r="B70" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="C70" s="125" t="s">
+      <c r="C70" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="D70" s="124"/>
-      <c r="E70" s="127" t="s">
+      <c r="D70" s="84"/>
+      <c r="E70" s="89" t="s">
         <v>172</v>
       </c>
       <c r="F70" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="G70" s="83" t="s">
+      <c r="G70" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H70" s="84" t="s">
+      <c r="H70" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I70" s="17"/>
@@ -19333,23 +19315,23 @@
       <c r="A71" s="6">
         <v>5</v>
       </c>
-      <c r="B71" s="124" t="s">
+      <c r="B71" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="125" t="s">
+      <c r="C71" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="D71" s="124"/>
-      <c r="E71" s="127" t="s">
+      <c r="D71" s="84"/>
+      <c r="E71" s="89" t="s">
         <v>173</v>
       </c>
       <c r="F71" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="G71" s="83" t="s">
+      <c r="G71" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H71" s="84" t="s">
+      <c r="H71" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I71" s="17"/>
@@ -19605,21 +19587,21 @@
       <c r="A72" s="6">
         <v>6</v>
       </c>
-      <c r="B72" s="124" t="s">
+      <c r="B72" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C72" s="125" t="s">
+      <c r="C72" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="124"/>
-      <c r="E72" s="127" t="s">
+      <c r="D72" s="84"/>
+      <c r="E72" s="89" t="s">
         <v>175</v>
       </c>
       <c r="F72" s="46"/>
-      <c r="G72" s="83" t="s">
+      <c r="G72" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="84" t="s">
+      <c r="H72" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I72" s="17"/>
@@ -19875,19 +19857,19 @@
       <c r="A73" s="6">
         <v>7</v>
       </c>
-      <c r="B73" s="124" t="s">
+      <c r="B73" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C73" s="125" t="s">
+      <c r="C73" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="D73" s="124"/>
-      <c r="E73" s="127" t="s">
+      <c r="D73" s="84"/>
+      <c r="E73" s="89" t="s">
         <v>198</v>
       </c>
       <c r="F73" s="46"/>
-      <c r="G73" s="83"/>
-      <c r="H73" s="84"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="42"/>
       <c r="I73" s="17"/>
       <c r="J73" s="77"/>
       <c r="K73" s="43"/>
@@ -20141,21 +20123,21 @@
       <c r="A74" s="6">
         <v>8</v>
       </c>
-      <c r="B74" s="124" t="s">
+      <c r="B74" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="C74" s="125" t="s">
+      <c r="C74" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="D74" s="124"/>
-      <c r="E74" s="127" t="s">
+      <c r="D74" s="84"/>
+      <c r="E74" s="89" t="s">
         <v>178</v>
       </c>
       <c r="F74" s="46"/>
-      <c r="G74" s="83" t="s">
+      <c r="G74" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H74" s="84" t="s">
+      <c r="H74" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I74" s="17"/>
@@ -20411,21 +20393,21 @@
       <c r="A75" s="6">
         <v>9</v>
       </c>
-      <c r="B75" s="124" t="s">
+      <c r="B75" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="125" t="s">
+      <c r="C75" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="D75" s="124"/>
-      <c r="E75" s="127" t="s">
+      <c r="D75" s="84"/>
+      <c r="E75" s="89" t="s">
         <v>183</v>
       </c>
       <c r="F75" s="46"/>
-      <c r="G75" s="83" t="s">
+      <c r="G75" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H75" s="84" t="s">
+      <c r="H75" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I75" s="17"/>
@@ -20681,19 +20663,19 @@
       <c r="A76" s="6">
         <v>10</v>
       </c>
-      <c r="B76" s="124" t="s">
+      <c r="B76" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="125" t="s">
+      <c r="C76" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="D76" s="124"/>
-      <c r="E76" s="126" t="s">
+      <c r="D76" s="84"/>
+      <c r="E76" s="89" t="s">
         <v>196</v>
       </c>
       <c r="F76" s="46"/>
-      <c r="G76" s="83"/>
-      <c r="H76" s="84"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="42"/>
       <c r="I76" s="17"/>
       <c r="J76" s="77"/>
       <c r="K76" s="43"/>
@@ -20947,21 +20929,21 @@
       <c r="A77" s="6">
         <v>11</v>
       </c>
-      <c r="B77" s="124" t="s">
+      <c r="B77" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C77" s="125" t="s">
+      <c r="C77" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="124"/>
-      <c r="E77" s="126" t="s">
+      <c r="D77" s="84"/>
+      <c r="E77" s="89" t="s">
         <v>179</v>
       </c>
       <c r="F77" s="46"/>
-      <c r="G77" s="83" t="s">
+      <c r="G77" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H77" s="84" t="s">
+      <c r="H77" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I77" s="17"/>
@@ -21217,21 +21199,21 @@
       <c r="A78" s="6">
         <v>12</v>
       </c>
-      <c r="B78" s="124" t="s">
+      <c r="B78" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C78" s="125" t="s">
+      <c r="C78" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="D78" s="124"/>
-      <c r="E78" s="126" t="s">
+      <c r="D78" s="84"/>
+      <c r="E78" s="89" t="s">
         <v>180</v>
       </c>
       <c r="F78" s="46"/>
-      <c r="G78" s="83" t="s">
+      <c r="G78" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H78" s="84" t="s">
+      <c r="H78" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I78" s="17"/>
@@ -21487,21 +21469,21 @@
       <c r="A79" s="6">
         <v>13</v>
       </c>
-      <c r="B79" s="124" t="s">
+      <c r="B79" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C79" s="125" t="s">
+      <c r="C79" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="D79" s="124"/>
-      <c r="E79" s="126" t="s">
+      <c r="D79" s="84"/>
+      <c r="E79" s="89" t="s">
         <v>199</v>
       </c>
       <c r="F79" s="46"/>
-      <c r="G79" s="83" t="s">
+      <c r="G79" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H79" s="84" t="s">
+      <c r="H79" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I79" s="17"/>
@@ -21757,21 +21739,21 @@
       <c r="A80" s="6">
         <v>14</v>
       </c>
-      <c r="B80" s="124" t="s">
+      <c r="B80" s="84" t="s">
         <v>181</v>
       </c>
-      <c r="C80" s="125" t="s">
+      <c r="C80" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="D80" s="124"/>
-      <c r="E80" s="127" t="s">
+      <c r="D80" s="84"/>
+      <c r="E80" s="89" t="s">
         <v>184</v>
       </c>
       <c r="F80" s="46"/>
-      <c r="G80" s="83" t="s">
+      <c r="G80" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H80" s="84" t="s">
+      <c r="H80" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I80" s="17"/>
@@ -22027,21 +22009,21 @@
       <c r="A81" s="6">
         <v>15</v>
       </c>
-      <c r="B81" s="124" t="s">
+      <c r="B81" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C81" s="125" t="s">
+      <c r="C81" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D81" s="124"/>
-      <c r="E81" s="127" t="s">
+      <c r="D81" s="84"/>
+      <c r="E81" s="89" t="s">
         <v>185</v>
       </c>
       <c r="F81" s="46"/>
-      <c r="G81" s="83" t="s">
+      <c r="G81" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H81" s="84" t="s">
+      <c r="H81" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I81" s="17"/>
@@ -22297,21 +22279,21 @@
       <c r="A82" s="6">
         <v>16</v>
       </c>
-      <c r="B82" s="124" t="s">
+      <c r="B82" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C82" s="125" t="s">
+      <c r="C82" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D82" s="124"/>
-      <c r="E82" s="127" t="s">
+      <c r="D82" s="84"/>
+      <c r="E82" s="89" t="s">
         <v>186</v>
       </c>
       <c r="F82" s="46"/>
-      <c r="G82" s="83" t="s">
+      <c r="G82" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="84" t="s">
+      <c r="H82" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I82" s="17"/>
@@ -22567,21 +22549,21 @@
       <c r="A83" s="6">
         <v>17</v>
       </c>
-      <c r="B83" s="124" t="s">
+      <c r="B83" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C83" s="125" t="s">
+      <c r="C83" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D83" s="124"/>
-      <c r="E83" s="127" t="s">
+      <c r="D83" s="84"/>
+      <c r="E83" s="89" t="s">
         <v>187</v>
       </c>
       <c r="F83" s="46"/>
-      <c r="G83" s="83" t="s">
+      <c r="G83" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H83" s="84" t="s">
+      <c r="H83" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I83" s="17"/>
@@ -22837,21 +22819,21 @@
       <c r="A84" s="6">
         <v>18</v>
       </c>
-      <c r="B84" s="124" t="s">
+      <c r="B84" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C84" s="125" t="s">
+      <c r="C84" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D84" s="124"/>
-      <c r="E84" s="127" t="s">
+      <c r="D84" s="84"/>
+      <c r="E84" s="89" t="s">
         <v>188</v>
       </c>
       <c r="F84" s="46"/>
-      <c r="G84" s="83" t="s">
+      <c r="G84" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H84" s="84" t="s">
+      <c r="H84" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I84" s="17"/>
@@ -23107,21 +23089,21 @@
       <c r="A85" s="6">
         <v>19</v>
       </c>
-      <c r="B85" s="124" t="s">
+      <c r="B85" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C85" s="125" t="s">
+      <c r="C85" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D85" s="124"/>
-      <c r="E85" s="127" t="s">
+      <c r="D85" s="84"/>
+      <c r="E85" s="89" t="s">
         <v>189</v>
       </c>
       <c r="F85" s="46"/>
-      <c r="G85" s="83" t="s">
+      <c r="G85" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H85" s="84" t="s">
+      <c r="H85" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I85" s="17"/>
@@ -23377,21 +23359,21 @@
       <c r="A86" s="6">
         <v>20</v>
       </c>
-      <c r="B86" s="124" t="s">
+      <c r="B86" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C86" s="125" t="s">
+      <c r="C86" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D86" s="124"/>
-      <c r="E86" s="127" t="s">
+      <c r="D86" s="84"/>
+      <c r="E86" s="89" t="s">
         <v>190</v>
       </c>
       <c r="F86" s="46"/>
-      <c r="G86" s="83" t="s">
+      <c r="G86" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H86" s="84" t="s">
+      <c r="H86" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I86" s="17"/>
@@ -23647,21 +23629,21 @@
       <c r="A87" s="6">
         <v>21</v>
       </c>
-      <c r="B87" s="124" t="s">
+      <c r="B87" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C87" s="125" t="s">
+      <c r="C87" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D87" s="124"/>
-      <c r="E87" s="127" t="s">
+      <c r="D87" s="84"/>
+      <c r="E87" s="89" t="s">
         <v>191</v>
       </c>
       <c r="F87" s="46"/>
-      <c r="G87" s="83" t="s">
+      <c r="G87" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H87" s="84" t="s">
+      <c r="H87" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I87" s="17"/>
@@ -23917,21 +23899,21 @@
       <c r="A88" s="6">
         <v>22</v>
       </c>
-      <c r="B88" s="124" t="s">
+      <c r="B88" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C88" s="125" t="s">
+      <c r="C88" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D88" s="124"/>
-      <c r="E88" s="127" t="s">
+      <c r="D88" s="84"/>
+      <c r="E88" s="89" t="s">
         <v>192</v>
       </c>
       <c r="F88" s="46"/>
-      <c r="G88" s="83" t="s">
+      <c r="G88" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H88" s="84" t="s">
+      <c r="H88" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I88" s="17"/>
@@ -24187,21 +24169,21 @@
       <c r="A89" s="6">
         <v>23</v>
       </c>
-      <c r="B89" s="124" t="s">
+      <c r="B89" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C89" s="125" t="s">
+      <c r="C89" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D89" s="124"/>
-      <c r="E89" s="127" t="s">
+      <c r="D89" s="84"/>
+      <c r="E89" s="89" t="s">
         <v>193</v>
       </c>
       <c r="F89" s="46"/>
-      <c r="G89" s="83" t="s">
+      <c r="G89" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H89" s="84" t="s">
+      <c r="H89" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I89" s="17"/>
@@ -24457,21 +24439,21 @@
       <c r="A90" s="6">
         <v>24</v>
       </c>
-      <c r="B90" s="124" t="s">
+      <c r="B90" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C90" s="125" t="s">
+      <c r="C90" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D90" s="124"/>
-      <c r="E90" s="127" t="s">
+      <c r="D90" s="84"/>
+      <c r="E90" s="89" t="s">
         <v>195</v>
       </c>
       <c r="F90" s="46"/>
-      <c r="G90" s="83" t="s">
+      <c r="G90" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H90" s="84" t="s">
+      <c r="H90" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I90" s="17"/>
@@ -24727,21 +24709,21 @@
       <c r="A91" s="6">
         <v>25</v>
       </c>
-      <c r="B91" s="124" t="s">
+      <c r="B91" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="C91" s="125" t="s">
+      <c r="C91" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="D91" s="124"/>
-      <c r="E91" s="127" t="s">
+      <c r="D91" s="84"/>
+      <c r="E91" s="89" t="s">
         <v>194</v>
       </c>
       <c r="F91" s="46"/>
-      <c r="G91" s="83" t="s">
+      <c r="G91" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="84" t="s">
+      <c r="H91" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I91" s="17"/>
@@ -24997,21 +24979,21 @@
       <c r="A92" s="6">
         <v>26</v>
       </c>
-      <c r="B92" s="124" t="s">
+      <c r="B92" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="C92" s="125" t="s">
+      <c r="C92" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="D92" s="124"/>
-      <c r="E92" s="127" t="s">
+      <c r="D92" s="84"/>
+      <c r="E92" s="89" t="s">
         <v>197</v>
       </c>
       <c r="F92" s="46"/>
-      <c r="G92" s="83" t="s">
+      <c r="G92" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H92" s="84" t="s">
+      <c r="H92" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I92" s="17"/>
@@ -25267,21 +25249,21 @@
       <c r="A93" s="6">
         <v>27</v>
       </c>
-      <c r="B93" s="124" t="s">
+      <c r="B93" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="C93" s="125" t="s">
+      <c r="C93" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="D93" s="124"/>
-      <c r="E93" s="127" t="s">
+      <c r="D93" s="84"/>
+      <c r="E93" s="89" t="s">
         <v>200</v>
       </c>
       <c r="F93" s="46"/>
-      <c r="G93" s="83" t="s">
+      <c r="G93" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H93" s="84" t="s">
+      <c r="H93" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I93" s="17"/>
@@ -25537,21 +25519,21 @@
       <c r="A94" s="6">
         <v>28</v>
       </c>
-      <c r="B94" s="124" t="s">
+      <c r="B94" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="C94" s="125" t="s">
+      <c r="C94" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="D94" s="124"/>
-      <c r="E94" s="127" t="s">
+      <c r="D94" s="84"/>
+      <c r="E94" s="89" t="s">
         <v>201</v>
       </c>
       <c r="F94" s="46"/>
-      <c r="G94" s="83" t="s">
+      <c r="G94" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H94" s="84" t="s">
+      <c r="H94" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I94" s="17"/>
@@ -25807,21 +25789,21 @@
       <c r="A95" s="6">
         <v>29</v>
       </c>
-      <c r="B95" s="124" t="s">
+      <c r="B95" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="C95" s="125" t="s">
+      <c r="C95" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="D95" s="124"/>
-      <c r="E95" s="127" t="s">
+      <c r="D95" s="84"/>
+      <c r="E95" s="89" t="s">
         <v>202</v>
       </c>
       <c r="F95" s="46"/>
-      <c r="G95" s="83" t="s">
+      <c r="G95" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H95" s="84" t="s">
+      <c r="H95" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I95" s="17"/>
@@ -26077,21 +26059,21 @@
       <c r="A96" s="6">
         <v>30</v>
       </c>
-      <c r="B96" s="124" t="s">
+      <c r="B96" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="125" t="s">
+      <c r="C96" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="D96" s="124"/>
-      <c r="E96" s="127" t="s">
+      <c r="D96" s="84"/>
+      <c r="E96" s="89" t="s">
         <v>203</v>
       </c>
       <c r="F96" s="46"/>
-      <c r="G96" s="83" t="s">
+      <c r="G96" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H96" s="84" t="s">
+      <c r="H96" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I96" s="17"/>
@@ -26347,21 +26329,21 @@
       <c r="A97" s="6">
         <v>31</v>
       </c>
-      <c r="B97" s="124" t="s">
+      <c r="B97" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="C97" s="125" t="s">
+      <c r="C97" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="D97" s="124"/>
-      <c r="E97" s="127" t="s">
+      <c r="D97" s="84"/>
+      <c r="E97" s="89" t="s">
         <v>204</v>
       </c>
       <c r="F97" s="46"/>
-      <c r="G97" s="83" t="s">
+      <c r="G97" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H97" s="84" t="s">
+      <c r="H97" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I97" s="17"/>
@@ -26617,21 +26599,21 @@
       <c r="A98" s="6">
         <v>32</v>
       </c>
-      <c r="B98" s="124" t="s">
+      <c r="B98" s="84" t="s">
         <v>206</v>
       </c>
-      <c r="C98" s="125" t="s">
+      <c r="C98" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="D98" s="124"/>
-      <c r="E98" s="127" t="s">
+      <c r="D98" s="84"/>
+      <c r="E98" s="89" t="s">
         <v>207</v>
       </c>
       <c r="F98" s="46"/>
-      <c r="G98" s="83" t="s">
+      <c r="G98" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H98" s="84" t="s">
+      <c r="H98" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I98" s="17"/>
@@ -26887,21 +26869,21 @@
       <c r="A99" s="6">
         <v>33</v>
       </c>
-      <c r="B99" s="124" t="s">
+      <c r="B99" s="84" t="s">
         <v>206</v>
       </c>
-      <c r="C99" s="125" t="s">
+      <c r="C99" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="D99" s="124"/>
-      <c r="E99" s="127" t="s">
+      <c r="D99" s="84"/>
+      <c r="E99" s="89" t="s">
         <v>208</v>
       </c>
       <c r="F99" s="46"/>
-      <c r="G99" s="83" t="s">
+      <c r="G99" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H99" s="84" t="s">
+      <c r="H99" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I99" s="17"/>
@@ -27157,21 +27139,21 @@
       <c r="A100" s="6">
         <v>34</v>
       </c>
-      <c r="B100" s="124" t="s">
+      <c r="B100" s="84" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="125" t="s">
+      <c r="C100" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="D100" s="124"/>
-      <c r="E100" s="127" t="s">
+      <c r="D100" s="84"/>
+      <c r="E100" s="89" t="s">
         <v>209</v>
       </c>
       <c r="F100" s="46"/>
-      <c r="G100" s="83" t="s">
+      <c r="G100" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="84" t="s">
+      <c r="H100" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I100" s="17"/>
@@ -27427,21 +27409,21 @@
       <c r="A101" s="6">
         <v>35</v>
       </c>
-      <c r="B101" s="124" t="s">
+      <c r="B101" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C101" s="125" t="s">
+      <c r="C101" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="124"/>
-      <c r="E101" s="127" t="s">
+      <c r="D101" s="84"/>
+      <c r="E101" s="89" t="s">
         <v>220</v>
       </c>
       <c r="F101" s="46"/>
-      <c r="G101" s="83" t="s">
+      <c r="G101" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H101" s="84" t="s">
+      <c r="H101" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I101" s="17"/>
@@ -27697,21 +27679,21 @@
       <c r="A102" s="6">
         <v>36</v>
       </c>
-      <c r="B102" s="124" t="s">
+      <c r="B102" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C102" s="125" t="s">
+      <c r="C102" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D102" s="124"/>
-      <c r="E102" s="127" t="s">
+      <c r="D102" s="84"/>
+      <c r="E102" s="89" t="s">
         <v>200</v>
       </c>
       <c r="F102" s="46"/>
-      <c r="G102" s="83" t="s">
+      <c r="G102" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H102" s="84" t="s">
+      <c r="H102" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I102" s="17"/>
@@ -27963,21 +27945,21 @@
       <c r="IU102" s="40"/>
       <c r="IV102" s="40"/>
     </row>
-    <row r="103" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:256" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
-      <c r="B103" s="124"/>
-      <c r="C103" s="125" t="s">
+      <c r="B103" s="84"/>
+      <c r="C103" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D103" s="124"/>
-      <c r="E103" s="127" t="s">
+      <c r="D103" s="84"/>
+      <c r="E103" s="89" t="s">
         <v>213</v>
       </c>
       <c r="F103" s="46"/>
-      <c r="G103" s="83" t="s">
+      <c r="G103" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H103" s="84" t="s">
+      <c r="H103" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I103" s="17"/>
@@ -28233,21 +28215,21 @@
       <c r="A104" s="6">
         <v>37</v>
       </c>
-      <c r="B104" s="124" t="s">
+      <c r="B104" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C104" s="125" t="s">
+      <c r="C104" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D104" s="124"/>
-      <c r="E104" s="127" t="s">
+      <c r="D104" s="84"/>
+      <c r="E104" s="89" t="s">
         <v>214</v>
       </c>
       <c r="F104" s="46"/>
-      <c r="G104" s="83" t="s">
+      <c r="G104" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H104" s="84" t="s">
+      <c r="H104" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I104" s="17"/>
@@ -28499,25 +28481,25 @@
       <c r="IU104" s="40"/>
       <c r="IV104" s="40"/>
     </row>
-    <row r="105" spans="1:256" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:256" s="37" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>38</v>
       </c>
-      <c r="B105" s="124" t="s">
+      <c r="B105" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C105" s="125" t="s">
+      <c r="C105" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D105" s="124"/>
-      <c r="E105" s="127" t="s">
+      <c r="D105" s="84"/>
+      <c r="E105" s="89" t="s">
         <v>215</v>
       </c>
       <c r="F105" s="46"/>
-      <c r="G105" s="83" t="s">
+      <c r="G105" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H105" s="84" t="s">
+      <c r="H105" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I105" s="17"/>
@@ -28773,21 +28755,21 @@
       <c r="A106" s="6">
         <v>39</v>
       </c>
-      <c r="B106" s="124" t="s">
+      <c r="B106" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C106" s="125" t="s">
+      <c r="C106" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D106" s="124"/>
-      <c r="E106" s="127" t="s">
+      <c r="D106" s="84"/>
+      <c r="E106" s="89" t="s">
         <v>216</v>
       </c>
       <c r="F106" s="46"/>
-      <c r="G106" s="83" t="s">
+      <c r="G106" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H106" s="84" t="s">
+      <c r="H106" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I106" s="17"/>
@@ -29043,21 +29025,21 @@
       <c r="A107" s="6">
         <v>40</v>
       </c>
-      <c r="B107" s="124" t="s">
+      <c r="B107" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C107" s="125" t="s">
+      <c r="C107" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="124"/>
-      <c r="E107" s="127" t="s">
+      <c r="D107" s="84"/>
+      <c r="E107" s="89" t="s">
         <v>217</v>
       </c>
       <c r="F107" s="46"/>
-      <c r="G107" s="83" t="s">
+      <c r="G107" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H107" s="84" t="s">
+      <c r="H107" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I107" s="17"/>
@@ -29313,21 +29295,21 @@
       <c r="A108" s="6">
         <v>41</v>
       </c>
-      <c r="B108" s="124" t="s">
+      <c r="B108" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C108" s="125" t="s">
+      <c r="C108" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D108" s="124"/>
-      <c r="E108" s="127" t="s">
+      <c r="D108" s="84"/>
+      <c r="E108" s="89" t="s">
         <v>219</v>
       </c>
       <c r="F108" s="46"/>
-      <c r="G108" s="83" t="s">
+      <c r="G108" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H108" s="84" t="s">
+      <c r="H108" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I108" s="17"/>
@@ -29583,21 +29565,21 @@
       <c r="A109" s="6">
         <v>42</v>
       </c>
-      <c r="B109" s="124" t="s">
+      <c r="B109" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C109" s="125" t="s">
+      <c r="C109" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="D109" s="124"/>
-      <c r="E109" s="127" t="s">
+      <c r="D109" s="84"/>
+      <c r="E109" s="89" t="s">
         <v>218</v>
       </c>
       <c r="F109" s="46"/>
-      <c r="G109" s="83" t="s">
+      <c r="G109" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H109" s="84" t="s">
+      <c r="H109" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I109" s="17"/>
@@ -29853,21 +29835,21 @@
       <c r="A110" s="6">
         <v>43</v>
       </c>
-      <c r="B110" s="124" t="s">
+      <c r="B110" s="84" t="s">
         <v>211</v>
       </c>
-      <c r="C110" s="125" t="s">
+      <c r="C110" s="88" t="s">
         <v>210</v>
       </c>
-      <c r="D110" s="124"/>
-      <c r="E110" s="127" t="s">
+      <c r="D110" s="84"/>
+      <c r="E110" s="89" t="s">
         <v>212</v>
       </c>
       <c r="F110" s="46"/>
-      <c r="G110" s="83" t="s">
+      <c r="G110" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H110" s="84" t="s">
+      <c r="H110" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I110" s="17"/>
@@ -30123,21 +30105,21 @@
       <c r="A111" s="6">
         <v>44</v>
       </c>
-      <c r="B111" s="124" t="s">
+      <c r="B111" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="C111" s="125" t="s">
+      <c r="C111" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="D111" s="124"/>
-      <c r="E111" s="127" t="s">
+      <c r="D111" s="84"/>
+      <c r="E111" s="89" t="s">
         <v>221</v>
       </c>
       <c r="F111" s="46"/>
-      <c r="G111" s="83" t="s">
+      <c r="G111" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H111" s="84" t="s">
+      <c r="H111" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I111" s="17"/>
@@ -30393,21 +30375,21 @@
       <c r="A112" s="6">
         <v>45</v>
       </c>
-      <c r="B112" s="124" t="s">
+      <c r="B112" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="C112" s="125" t="s">
+      <c r="C112" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="D112" s="124"/>
-      <c r="E112" s="127" t="s">
+      <c r="D112" s="84"/>
+      <c r="E112" s="89" t="s">
         <v>223</v>
       </c>
       <c r="F112" s="46"/>
-      <c r="G112" s="83" t="s">
+      <c r="G112" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H112" s="84" t="s">
+      <c r="H112" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I112" s="17"/>
@@ -30663,21 +30645,21 @@
       <c r="A113" s="6">
         <v>46</v>
       </c>
-      <c r="B113" s="124" t="s">
+      <c r="B113" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="125" t="s">
+      <c r="C113" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="124"/>
-      <c r="E113" s="127" t="s">
+      <c r="D113" s="84"/>
+      <c r="E113" s="89" t="s">
         <v>222</v>
       </c>
       <c r="F113" s="46"/>
-      <c r="G113" s="83" t="s">
+      <c r="G113" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H113" s="84" t="s">
+      <c r="H113" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I113" s="17"/>
@@ -30933,23 +30915,23 @@
       <c r="A114" s="6">
         <v>47</v>
       </c>
-      <c r="B114" s="124" t="s">
+      <c r="B114" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C114" s="125" t="s">
+      <c r="C114" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="D114" s="124"/>
-      <c r="E114" s="127" t="s">
+      <c r="D114" s="84"/>
+      <c r="E114" s="89" t="s">
         <v>225</v>
       </c>
       <c r="F114" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="G114" s="83" t="s">
+      <c r="G114" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H114" s="84" t="s">
+      <c r="H114" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I114" s="17"/>
@@ -31205,23 +31187,23 @@
       <c r="A115" s="6">
         <v>48</v>
       </c>
-      <c r="B115" s="124" t="s">
+      <c r="B115" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C115" s="125" t="s">
+      <c r="C115" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="D115" s="124" t="s">
+      <c r="D115" s="84" t="s">
         <v>227</v>
       </c>
-      <c r="E115" s="127" t="s">
+      <c r="E115" s="89" t="s">
         <v>228</v>
       </c>
       <c r="F115" s="46"/>
-      <c r="G115" s="83" t="s">
+      <c r="G115" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H115" s="84" t="s">
+      <c r="H115" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I115" s="17"/>
@@ -31477,21 +31459,21 @@
       <c r="A116" s="6">
         <v>49</v>
       </c>
-      <c r="B116" s="124" t="s">
+      <c r="B116" s="84" t="s">
         <v>224</v>
       </c>
-      <c r="C116" s="125" t="s">
+      <c r="C116" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D116" s="124"/>
-      <c r="E116" s="126" t="s">
+      <c r="D116" s="84"/>
+      <c r="E116" s="89" t="s">
         <v>179</v>
       </c>
       <c r="F116" s="46"/>
-      <c r="G116" s="83" t="s">
+      <c r="G116" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H116" s="84" t="s">
+      <c r="H116" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I116" s="17"/>
@@ -31747,21 +31729,21 @@
       <c r="A117" s="6">
         <v>50</v>
       </c>
-      <c r="B117" s="124" t="s">
+      <c r="B117" s="84" t="s">
         <v>224</v>
       </c>
-      <c r="C117" s="125" t="s">
+      <c r="C117" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D117" s="124"/>
-      <c r="E117" s="126" t="s">
+      <c r="D117" s="84"/>
+      <c r="E117" s="89" t="s">
         <v>199</v>
       </c>
       <c r="F117" s="46"/>
-      <c r="G117" s="83" t="s">
+      <c r="G117" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H117" s="84" t="s">
+      <c r="H117" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I117" s="17"/>
@@ -32017,14 +31999,14 @@
       <c r="A118" s="6">
         <v>51</v>
       </c>
-      <c r="B118" s="124" t="s">
+      <c r="B118" s="84" t="s">
         <v>145</v>
       </c>
-      <c r="C118" s="125" t="s">
+      <c r="C118" s="88" t="s">
         <v>146</v>
       </c>
-      <c r="D118" s="124"/>
-      <c r="E118" s="127" t="s">
+      <c r="D118" s="84"/>
+      <c r="E118" s="89" t="s">
         <v>229</v>
       </c>
       <c r="F118" s="46"/>
@@ -32283,27 +32265,27 @@
       <c r="A119" s="6">
         <v>52</v>
       </c>
-      <c r="B119" s="120" t="s">
+      <c r="B119" s="84" t="s">
         <v>230</v>
       </c>
-      <c r="C119" s="117" t="s">
+      <c r="C119" s="81" t="s">
         <v>231</v>
       </c>
-      <c r="D119" s="115" t="s">
+      <c r="D119" s="79" t="s">
         <v>232</v>
       </c>
-      <c r="E119" s="128" t="s">
+      <c r="E119" s="90" t="s">
         <v>233</v>
       </c>
       <c r="F119" s="46"/>
-      <c r="G119" s="117" t="s">
+      <c r="G119" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="H119" s="123" t="s">
+      <c r="H119" s="87" t="s">
         <v>248</v>
       </c>
       <c r="I119" s="17"/>
-      <c r="J119" s="78"/>
+      <c r="J119" s="77"/>
       <c r="K119" s="43"/>
       <c r="L119" s="16"/>
       <c r="M119" s="16"/>
@@ -32555,27 +32537,27 @@
       <c r="A120" s="6">
         <v>53</v>
       </c>
-      <c r="B120" s="120" t="s">
+      <c r="B120" s="84" t="s">
         <v>230</v>
       </c>
-      <c r="C120" s="114" t="s">
+      <c r="C120" s="78" t="s">
         <v>231</v>
       </c>
-      <c r="D120" s="115" t="s">
+      <c r="D120" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="E120" s="128" t="s">
+      <c r="E120" s="90" t="s">
         <v>251</v>
       </c>
       <c r="F120" s="46"/>
-      <c r="G120" s="117" t="s">
+      <c r="G120" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="H120" s="123" t="s">
+      <c r="H120" s="87" t="s">
         <v>248</v>
       </c>
       <c r="I120" s="17"/>
-      <c r="J120" s="78"/>
+      <c r="J120" s="77"/>
       <c r="K120" s="43"/>
       <c r="L120" s="16"/>
       <c r="M120" s="16"/>
@@ -32823,31 +32805,31 @@
       <c r="IU120" s="40"/>
       <c r="IV120" s="40"/>
     </row>
-    <row r="121" spans="1:256" s="37" customFormat="1" ht="210" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:256" s="37" customFormat="1" ht="225" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>54</v>
       </c>
-      <c r="B121" s="129" t="s">
+      <c r="B121" s="91" t="s">
         <v>235</v>
       </c>
-      <c r="C121" s="117" t="s">
+      <c r="C121" s="81" t="s">
         <v>144</v>
       </c>
-      <c r="D121" s="116" t="s">
+      <c r="D121" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="E121" s="128" t="s">
+      <c r="E121" s="90" t="s">
         <v>252</v>
       </c>
       <c r="F121" s="46"/>
-      <c r="G121" s="117" t="s">
+      <c r="G121" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="H121" s="123" t="s">
+      <c r="H121" s="87" t="s">
         <v>248</v>
       </c>
       <c r="I121" s="17"/>
-      <c r="J121" s="78"/>
+      <c r="J121" s="77"/>
       <c r="K121" s="43"/>
       <c r="L121" s="16"/>
       <c r="M121" s="16"/>
@@ -33099,27 +33081,27 @@
       <c r="A122" s="6">
         <v>55</v>
       </c>
-      <c r="B122" s="120" t="s">
+      <c r="B122" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="C122" s="117" t="s">
+      <c r="C122" s="81" t="s">
         <v>236</v>
       </c>
-      <c r="D122" s="115" t="s">
+      <c r="D122" s="79" t="s">
         <v>237</v>
       </c>
-      <c r="E122" s="128" t="s">
+      <c r="E122" s="90" t="s">
         <v>238</v>
       </c>
       <c r="F122" s="46"/>
-      <c r="G122" s="117" t="s">
+      <c r="G122" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="H122" s="123" t="s">
+      <c r="H122" s="87" t="s">
         <v>248</v>
       </c>
       <c r="I122" s="17"/>
-      <c r="J122" s="78"/>
+      <c r="J122" s="77"/>
       <c r="K122" s="43"/>
       <c r="L122" s="16"/>
       <c r="M122" s="16"/>
@@ -33371,25 +33353,25 @@
       <c r="A123" s="6">
         <v>56</v>
       </c>
-      <c r="B123" s="120" t="s">
+      <c r="B123" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="C123" s="118" t="s">
+      <c r="C123" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="D123" s="115"/>
-      <c r="E123" s="128" t="s">
+      <c r="D123" s="79"/>
+      <c r="E123" s="90" t="s">
         <v>253</v>
       </c>
       <c r="F123" s="46"/>
-      <c r="G123" s="117" t="s">
+      <c r="G123" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="H123" s="123" t="s">
+      <c r="H123" s="87" t="s">
         <v>248</v>
       </c>
       <c r="I123" s="17"/>
-      <c r="J123" s="78"/>
+      <c r="J123" s="77"/>
       <c r="K123" s="43"/>
       <c r="L123" s="16"/>
       <c r="M123" s="16"/>
@@ -33641,25 +33623,25 @@
       <c r="A124" s="6">
         <v>57</v>
       </c>
-      <c r="B124" s="120" t="s">
+      <c r="B124" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="C124" s="119" t="s">
+      <c r="C124" s="83" t="s">
         <v>241</v>
       </c>
-      <c r="D124" s="120"/>
-      <c r="E124" s="121" t="s">
+      <c r="D124" s="84"/>
+      <c r="E124" s="85" t="s">
         <v>242</v>
       </c>
       <c r="F124" s="46"/>
-      <c r="G124" s="117" t="s">
+      <c r="G124" s="81" t="s">
         <v>249</v>
       </c>
-      <c r="H124" s="123" t="s">
+      <c r="H124" s="87" t="s">
         <v>250</v>
       </c>
       <c r="I124" s="17"/>
-      <c r="J124" s="78"/>
+      <c r="J124" s="77"/>
       <c r="K124" s="43"/>
       <c r="L124" s="16"/>
       <c r="M124" s="16"/>
@@ -33911,25 +33893,25 @@
       <c r="A125" s="6">
         <v>58</v>
       </c>
-      <c r="B125" s="120" t="s">
+      <c r="B125" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="C125" s="122" t="s">
+      <c r="C125" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="D125" s="120"/>
-      <c r="E125" s="121" t="s">
+      <c r="D125" s="84"/>
+      <c r="E125" s="85" t="s">
         <v>244</v>
       </c>
       <c r="F125" s="46"/>
-      <c r="G125" s="117" t="s">
+      <c r="G125" s="81" t="s">
         <v>249</v>
       </c>
-      <c r="H125" s="123" t="s">
+      <c r="H125" s="87" t="s">
         <v>250</v>
       </c>
       <c r="I125" s="17"/>
-      <c r="J125" s="78"/>
+      <c r="J125" s="77"/>
       <c r="K125" s="43"/>
       <c r="L125" s="16"/>
       <c r="M125" s="16"/>
@@ -34181,25 +34163,25 @@
       <c r="A126" s="6">
         <v>59</v>
       </c>
-      <c r="B126" s="120" t="s">
+      <c r="B126" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="C126" s="122" t="s">
+      <c r="C126" s="86" t="s">
         <v>245</v>
       </c>
-      <c r="D126" s="120"/>
-      <c r="E126" s="121" t="s">
+      <c r="D126" s="84"/>
+      <c r="E126" s="85" t="s">
         <v>246</v>
       </c>
       <c r="F126" s="46"/>
-      <c r="G126" s="117" t="s">
+      <c r="G126" s="81" t="s">
         <v>249</v>
       </c>
-      <c r="H126" s="123" t="s">
+      <c r="H126" s="87" t="s">
         <v>250</v>
       </c>
       <c r="I126" s="17"/>
-      <c r="J126" s="78"/>
+      <c r="J126" s="77"/>
       <c r="K126" s="43"/>
       <c r="L126" s="16"/>
       <c r="M126" s="16"/>
@@ -34746,10 +34728,10 @@
       <c r="J129" s="10"/>
       <c r="K129" s="11"/>
       <c r="L129" s="11"/>
-      <c r="M129" s="88" t="s">
+      <c r="M129" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="N129" s="88"/>
+      <c r="N129" s="96"/>
       <c r="O129" s="10"/>
       <c r="P129" s="11"/>
       <c r="Q129" s="11"/>
@@ -37891,47 +37873,25 @@
       <c r="E146" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A11:IV118"/>
+  <autoFilter ref="A11:IV118" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <customSheetViews>
-    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
-      <selection activeCell="F21" sqref="F21"/>
+    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
+      <selection activeCell="C63" sqref="C63:D63"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-      <autoFilter ref="B9:Y31"/>
+      <autoFilter ref="B9:Y51" xr:uid="{BD90CFC3-2952-4639-8BCA-B5FAAE7E7B6F}"/>
     </customSheetView>
-    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
-      <selection activeCell="K20" sqref="K20"/>
+    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
+      <selection activeCell="K12" sqref="K12"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="B9:Y31"/>
-    </customSheetView>
-    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
-      <selection activeCell="K23" sqref="K23"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId3"/>
-      <autoFilter ref="B9:Y31"/>
-    </customSheetView>
-    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
-      <selection activeCell="C238" sqref="C238:D238"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="B10:Z230">
-        <filterColumn colId="7">
-          <filters>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
-            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
-          </filters>
-        </filterColumn>
-      </autoFilter>
+      <autoFilter ref="B9:Y31" xr:uid="{CD628563-407D-4066-9332-4649444E5942}"/>
     </customSheetView>
     <customSheetView guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" topLeftCell="K144">
       <selection activeCell="O76" sqref="O76"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId5"/>
-      <autoFilter ref="B10:Z230">
+      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+      <autoFilter ref="B10:Z230" xr:uid="{116642BE-3ACD-42E1-8CD8-03BB2FAB43BD}">
         <filterColumn colId="7">
           <filters>
             <filter val="ИГН, ГТЭП"/>
@@ -37947,29 +37907,48 @@
         </filterColumn>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
-      <selection activeCell="K12" sqref="K12"/>
+    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
+      <selection activeCell="C238" sqref="C238:D238"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
+      <autoFilter ref="B10:Z230" xr:uid="{3D0227F2-0076-4869-907F-803FDADF1B5E}">
+        <filterColumn colId="7">
+          <filters>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
+            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
+          </filters>
+        </filterColumn>
+      </autoFilter>
+    </customSheetView>
+    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
+      <selection activeCell="K23" sqref="K23"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId5"/>
+      <autoFilter ref="B9:Y31" xr:uid="{EC91F4EF-7755-4C2C-80A8-79A5A4AA55E2}"/>
+    </customSheetView>
+    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
+      <selection activeCell="K20" sqref="K20"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="B9:Y31"/>
+      <autoFilter ref="B9:Y31" xr:uid="{6D341D86-55EE-44DB-83F3-215DB7234690}"/>
     </customSheetView>
-    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
-      <selection activeCell="C63" sqref="C63:D63"/>
+    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
+      <selection activeCell="F21" sqref="F21"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId7"/>
-      <autoFilter ref="B9:Y51"/>
+      <autoFilter ref="B9:Y31" xr:uid="{008637D3-23C4-4135-B161-2D5BC3E2CBD9}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="31">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="M129:N129"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="A8:A9"/>
@@ -37986,25 +37965,28 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I10:K10"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12:I37 I67:I127">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12:I37 I67:I127" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$B$131:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:N37 N67:N127 N39:N65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:N37 N67:N127 N39:N65" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$B$135:$B$136</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L37 L67:L127 L39:L65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L37 L67:L127 L39:L65" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$B$138:$B$140</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I39:I65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I39:I65" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>$B$64:$B$66</formula1>
     </dataValidation>
   </dataValidations>
@@ -38020,7 +38002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -38081,11 +38063,11 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -38108,12 +38090,12 @@
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
@@ -38135,11 +38117,11 @@
       <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="48"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -38162,12 +38144,12 @@
       <c r="W4" s="3"/>
     </row>
     <row r="5" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -38241,39 +38223,39 @@
       <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:255" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="112" t="s">
+      <c r="A8" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="92" t="s">
+      <c r="D8" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="92" t="s">
+      <c r="F8" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="109" t="s">
+      <c r="G8" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="92" t="s">
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="92"/>
-      <c r="M8" s="95" t="s">
+      <c r="L8" s="93"/>
+      <c r="M8" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="95"/>
-      <c r="O8" s="89" t="s">
+      <c r="N8" s="94"/>
+      <c r="O8" s="97" t="s">
         <v>30</v>
       </c>
       <c r="P8" s="34" t="s">
@@ -38298,22 +38280,22 @@
       </c>
     </row>
     <row r="9" spans="1:255" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="113"/>
-      <c r="B9" s="108"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
+      <c r="A9" s="119"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
       <c r="G9" s="25" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="109" t="s">
+      <c r="I9" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="110"/>
+      <c r="J9" s="111"/>
       <c r="K9" s="19" t="s">
         <v>8</v>
       </c>
@@ -38326,7 +38308,7 @@
       <c r="N9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="90"/>
+      <c r="O9" s="98"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="35" t="s">
         <v>6</v>
@@ -38347,28 +38329,28 @@
       </c>
     </row>
     <row r="10" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="98" t="s">
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="87" t="s">
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="87"/>
-      <c r="M10" s="86" t="s">
+      <c r="L10" s="102"/>
+      <c r="M10" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="N10" s="86"/>
+      <c r="N10" s="103"/>
       <c r="O10" s="47" t="s">
         <v>17</v>
       </c>
@@ -38392,8 +38374,8 @@
       <c r="F11" s="59"/>
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="102"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="114"/>
       <c r="K11" s="6"/>
       <c r="L11" s="16"/>
       <c r="M11" s="71"/>
@@ -38651,8 +38633,8 @@
       <c r="F12" s="59"/>
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="102"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="114"/>
       <c r="K12" s="6"/>
       <c r="L12" s="16"/>
       <c r="M12" s="71"/>
@@ -38910,8 +38892,8 @@
       <c r="F13" s="59"/>
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="102"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="114"/>
       <c r="K13" s="6"/>
       <c r="L13" s="16"/>
       <c r="M13" s="71"/>
@@ -39169,8 +39151,8 @@
       <c r="F14" s="59"/>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="102"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="114"/>
       <c r="K14" s="6"/>
       <c r="L14" s="16"/>
       <c r="M14" s="71"/>
@@ -39428,8 +39410,8 @@
       <c r="F15" s="59"/>
       <c r="G15" s="70"/>
       <c r="H15" s="70"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="102"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="114"/>
       <c r="K15" s="6"/>
       <c r="L15" s="16"/>
       <c r="M15" s="71"/>
@@ -39677,28 +39659,28 @@
       <c r="IU15" s="40"/>
     </row>
     <row r="16" spans="1:255" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="98" t="s">
+      <c r="B16" s="106"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="87" t="s">
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="L16" s="87"/>
-      <c r="M16" s="86" t="s">
+      <c r="L16" s="102"/>
+      <c r="M16" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="86"/>
+      <c r="N16" s="103"/>
       <c r="O16" s="47" t="s">
         <v>17</v>
       </c>
@@ -39956,8 +39938,8 @@
       <c r="F17" s="59"/>
       <c r="G17" s="70"/>
       <c r="H17" s="70"/>
-      <c r="I17" s="101"/>
-      <c r="J17" s="102"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="114"/>
       <c r="K17" s="6"/>
       <c r="L17" s="16"/>
       <c r="M17" s="71"/>
@@ -40215,8 +40197,8 @@
       <c r="F18" s="59"/>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
-      <c r="I18" s="101"/>
-      <c r="J18" s="102"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="114"/>
       <c r="K18" s="6"/>
       <c r="L18" s="16"/>
       <c r="M18" s="71"/>
@@ -40725,18 +40707,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="63"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
       <c r="E20" s="7"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="10"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-      <c r="K20" s="88" t="s">
+      <c r="K20" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="88"/>
+      <c r="L20" s="96"/>
       <c r="M20" s="23"/>
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
@@ -40994,8 +40976,8 @@
       <c r="H21" s="10"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="88"/>
-      <c r="L21" s="88"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
       <c r="M21" s="23"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
@@ -43350,8 +43332,25 @@
       <c r="D33" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="K1:K33"/>
+  <autoFilter ref="K1:K33" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="33">
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B8:B9"/>
@@ -43368,23 +43367,6 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M8:N8"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:K15">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
@@ -43397,16 +43379,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K19" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G15 G17:G18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G15 G17:G18" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>$B$22:$B$24</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11:K15 K17:K18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11:K15 K17:K18" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>$B$29:$B$31</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M11:M15 M17:M18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M11:M15 M17:M18" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>$B$26:$B$27</formula1>
     </dataValidation>
   </dataValidations>
